--- a/Documents/SETK-TR-F1H26-Translation_Document.xlsx
+++ b/Documents/SETK-TR-F1H26-Translation_Document.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dilara.tek\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Adobe-Form-Builder-main\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BB1DA6-D8C5-4D61-9219-E5CD9BBF48EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F191027F-1A59-4ECA-811F-A392C0017055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Translations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="197">
   <si>
     <t>Translation</t>
   </si>
@@ -628,6 +628,12 @@
   </si>
   <si>
     <t>At the bottom please provide "Informative Text" and "Campaign T&amp;C" links as we did in previous launches.</t>
+  </si>
+  <si>
+    <t>Project Code</t>
+  </si>
+  <si>
+    <t>F1H26</t>
   </si>
 </sst>
 </file>
@@ -843,12 +849,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -860,6 +860,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1168,16 +1174,20 @@
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="17"/>
-      <c r="B2"/>
-      <c r="C2" s="18"/>
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>196</v>
+      </c>
       <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="30"/>
+      <c r="C3" s="36"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
@@ -1243,7 +1253,7 @@
       <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="30" t="s">
         <v>147</v>
       </c>
       <c r="D10" s="14"/>
@@ -1317,7 +1327,7 @@
       <c r="B17" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="29" t="s">
         <v>152</v>
       </c>
       <c r="D17" s="16"/>
@@ -1389,7 +1399,7 @@
       <c r="B23" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="31" t="s">
         <v>157</v>
       </c>
       <c r="D23" s="14"/>
@@ -1529,7 +1539,7 @@
       <c r="B36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="29" t="s">
         <v>152</v>
       </c>
       <c r="D36" s="16"/>
@@ -1897,10 +1907,10 @@
       <c r="B74" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="D74" s="36" t="s">
+      <c r="D74" s="34" t="s">
         <v>194</v>
       </c>
     </row>
@@ -1943,7 +1953,7 @@
       <c r="B78" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="33" t="s">
         <v>189</v>
       </c>
       <c r="D78" s="14"/>
